--- a/Tagihan/2026/Agustus/Mbg Flamboyan.xlsx
+++ b/Tagihan/2026/Agustus/Mbg Flamboyan.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\Data-Pekerjaan\Tagihan\2026\Agustus\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Data Pekerjaan\Tagihan\2026\Agustus\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7AC185DA-0F86-4650-BD1A-1418EE23A542}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9FCA1F01-8371-456C-9210-6DD63E7582AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Perbaikan" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="42">
   <si>
     <t>NO.</t>
   </si>
@@ -193,11 +193,29 @@
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t xml:space="preserve"> 07 Agustus 2026</t>
+      <t xml:space="preserve"> 05 Agustus 2025</t>
     </r>
   </si>
   <si>
-    <t>Biaya Perbaikan CCTV</t>
+    <t>Kabel Listrik</t>
+  </si>
+  <si>
+    <t>Kabel LAN</t>
+  </si>
+  <si>
+    <t>Konektor RJ45</t>
+  </si>
+  <si>
+    <t>Steker Female</t>
+  </si>
+  <si>
+    <t>Steker Broco Bulat</t>
+  </si>
+  <si>
+    <t>Barel UTP</t>
+  </si>
+  <si>
+    <t>Perbaikan Dan Reposisi Camera</t>
   </si>
 </sst>
 </file>
@@ -205,7 +223,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="_-&quot;Rp&quot;* #,##0_-;\-&quot;Rp&quot;* #,##0_-;_-&quot;Rp&quot;* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="42" formatCode="_-&quot;Rp&quot;* #,##0_-;\-&quot;Rp&quot;* #,##0_-;_-&quot;Rp&quot;* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
   <fonts count="11" x14ac:knownFonts="1">
     <font>
@@ -558,38 +576,38 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="42" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="42" fontId="10" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -640,7 +658,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -661,11 +679,11 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -743,13 +761,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>238125</xdr:colOff>
-      <xdr:row>33</xdr:row>
+      <xdr:row>32</xdr:row>
       <xdr:rowOff>59532</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>2403475</xdr:colOff>
-      <xdr:row>40</xdr:row>
+      <xdr:row>39</xdr:row>
       <xdr:rowOff>115571</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1247,7 +1265,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B5:H41"/>
+  <dimension ref="B5:H40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.28515625" customWidth="1"/>
@@ -1360,66 +1378,144 @@
         <v>35</v>
       </c>
       <c r="D17" s="34">
+        <v>21</v>
+      </c>
+      <c r="E17" s="33" t="s">
+        <v>21</v>
+      </c>
+      <c r="F17" s="25">
+        <v>6000</v>
+      </c>
+      <c r="G17" s="25">
+        <f>F17*D17</f>
+        <v>126000</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="2">
+        <v>2</v>
+      </c>
+      <c r="C18" s="37" t="s">
+        <v>36</v>
+      </c>
+      <c r="D18" s="2">
+        <v>6</v>
+      </c>
+      <c r="E18" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="F18" s="25">
+        <v>5000</v>
+      </c>
+      <c r="G18" s="25">
+        <f t="shared" ref="G18:G23" si="0">F18*D18</f>
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="2">
+        <v>3</v>
+      </c>
+      <c r="C19" s="37" t="s">
+        <v>37</v>
+      </c>
+      <c r="D19" s="2">
+        <v>9</v>
+      </c>
+      <c r="E19" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="F19" s="25">
+        <v>5000</v>
+      </c>
+      <c r="G19" s="25">
+        <f t="shared" si="0"/>
+        <v>45000</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="2">
+        <v>4</v>
+      </c>
+      <c r="C20" s="37" t="s">
+        <v>38</v>
+      </c>
+      <c r="D20" s="2">
+        <v>3</v>
+      </c>
+      <c r="E20" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="F20" s="25">
+        <v>5000</v>
+      </c>
+      <c r="G20" s="25">
+        <f t="shared" si="0"/>
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="2">
+        <v>5</v>
+      </c>
+      <c r="C21" s="26" t="s">
+        <v>39</v>
+      </c>
+      <c r="D21" s="2">
         <v>1</v>
       </c>
-      <c r="E17" s="34" t="s">
+      <c r="E21" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="F21" s="23">
+        <v>12000</v>
+      </c>
+      <c r="G21" s="25">
+        <f t="shared" si="0"/>
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="2">
+        <v>6</v>
+      </c>
+      <c r="C22" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="D22" s="2">
+        <v>2</v>
+      </c>
+      <c r="E22" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="F22" s="23">
+        <v>5000</v>
+      </c>
+      <c r="G22" s="25">
+        <f t="shared" si="0"/>
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="2">
+        <v>7</v>
+      </c>
+      <c r="C23" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="D23" s="2">
+        <v>7</v>
+      </c>
+      <c r="E23" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="F17" s="25">
+      <c r="F23" s="23">
         <v>100000</v>
       </c>
-      <c r="G17" s="25">
-        <f t="shared" ref="G17:G18" si="0">F17*D17</f>
-        <v>100000</v>
-      </c>
-    </row>
-    <row r="18" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="2"/>
-      <c r="C18" s="37"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="25"/>
-      <c r="G18" s="25"/>
-    </row>
-    <row r="19" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="2"/>
-      <c r="C19" s="37"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="25"/>
-      <c r="G19" s="25"/>
-    </row>
-    <row r="20" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="2"/>
-      <c r="C20" s="37"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="26"/>
-      <c r="F20" s="25"/>
-      <c r="G20" s="25"/>
-    </row>
-    <row r="21" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="2"/>
-      <c r="C21" s="26"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="26"/>
-      <c r="F21" s="25"/>
-      <c r="G21" s="25"/>
-    </row>
-    <row r="22" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="2"/>
-      <c r="C22" s="26"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="26"/>
-      <c r="F22" s="23"/>
-      <c r="G22" s="25"/>
-    </row>
-    <row r="23" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="2"/>
-      <c r="C23" s="26"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="26"/>
-      <c r="F23" s="23"/>
-      <c r="G23" s="25"/>
+      <c r="G23" s="25">
+        <f t="shared" si="0"/>
+        <v>700000</v>
+      </c>
     </row>
     <row r="24" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="2"/>
@@ -1473,93 +1569,85 @@
       <c r="B30" s="2"/>
       <c r="C30" s="26"/>
       <c r="D30" s="2"/>
-      <c r="E30" s="26"/>
-      <c r="F30" s="23"/>
-      <c r="G30" s="25"/>
-    </row>
-    <row r="31" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="2"/>
-      <c r="C31" s="26"/>
-      <c r="D31" s="2"/>
-      <c r="E31" s="28"/>
-      <c r="F31" s="25"/>
-      <c r="G31" s="24"/>
-    </row>
-    <row r="32" spans="2:7" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="47" t="s">
+      <c r="E30" s="28"/>
+      <c r="F30" s="25"/>
+      <c r="G30" s="24"/>
+    </row>
+    <row r="31" spans="2:7" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B31" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="C32" s="48"/>
-      <c r="D32" s="48"/>
-      <c r="E32" s="48"/>
-      <c r="F32" s="49"/>
-      <c r="G32" s="27">
-        <f>SUM(G17:G31)</f>
-        <v>100000</v>
-      </c>
-    </row>
-    <row r="33" spans="2:8" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="3"/>
-      <c r="C33" s="3"/>
-      <c r="D33" s="31"/>
-      <c r="E33" s="3"/>
-      <c r="F33" s="16"/>
-      <c r="G33" s="17"/>
-    </row>
-    <row r="35" spans="2:8" s="19" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B35" s="50" t="s">
+      <c r="C31" s="48"/>
+      <c r="D31" s="48"/>
+      <c r="E31" s="48"/>
+      <c r="F31" s="49"/>
+      <c r="G31" s="27">
+        <f>SUM(G17:G30)</f>
+        <v>938000</v>
+      </c>
+    </row>
+    <row r="32" spans="2:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="3"/>
+      <c r="C32" s="3"/>
+      <c r="D32" s="31"/>
+      <c r="E32" s="3"/>
+      <c r="F32" s="16"/>
+      <c r="G32" s="17"/>
+    </row>
+    <row r="34" spans="2:8" s="19" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="B34" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="C35" s="50"/>
-      <c r="D35" s="32"/>
-      <c r="E35" s="18"/>
-      <c r="F35" s="51" t="s">
+      <c r="C34" s="50"/>
+      <c r="D34" s="32"/>
+      <c r="E34" s="18"/>
+      <c r="F34" s="51" t="s">
         <v>6</v>
       </c>
-      <c r="G35" s="51"/>
-    </row>
-    <row r="39" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B39" s="41"/>
-      <c r="C39" s="41"/>
-      <c r="D39" s="41"/>
-      <c r="E39" s="41"/>
-      <c r="F39" s="41"/>
-      <c r="G39" s="41"/>
+      <c r="G34" s="51"/>
+    </row>
+    <row r="38" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B38" s="41"/>
+      <c r="C38" s="41"/>
+      <c r="D38" s="41"/>
+      <c r="E38" s="41"/>
+      <c r="F38" s="41"/>
+      <c r="G38" s="41"/>
+    </row>
+    <row r="39" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B39" s="45" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39" s="46"/>
+      <c r="D39" s="46"/>
+      <c r="E39" s="46"/>
+      <c r="F39" s="20"/>
+      <c r="G39" s="22"/>
+      <c r="H39" s="21"/>
     </row>
     <row r="40" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B40" s="45" t="s">
-        <v>14</v>
-      </c>
-      <c r="C40" s="46"/>
-      <c r="D40" s="46"/>
-      <c r="E40" s="46"/>
-      <c r="F40" s="20"/>
-      <c r="G40" s="22"/>
+      <c r="B40" s="42" t="s">
+        <v>15</v>
+      </c>
+      <c r="C40" s="43"/>
+      <c r="D40" s="43"/>
+      <c r="E40" s="43"/>
+      <c r="F40" s="43"/>
+      <c r="G40" s="43"/>
       <c r="H40" s="21"/>
-    </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B41" s="42" t="s">
-        <v>15</v>
-      </c>
-      <c r="C41" s="43"/>
-      <c r="D41" s="43"/>
-      <c r="E41" s="43"/>
-      <c r="F41" s="43"/>
-      <c r="G41" s="43"/>
-      <c r="H41" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="13">
     <mergeCell ref="C7:G8"/>
     <mergeCell ref="C9:G9"/>
     <mergeCell ref="C10:G10"/>
-    <mergeCell ref="B39:G39"/>
-    <mergeCell ref="B41:G41"/>
+    <mergeCell ref="B38:G38"/>
+    <mergeCell ref="B40:G40"/>
     <mergeCell ref="C11:G11"/>
-    <mergeCell ref="B40:E40"/>
-    <mergeCell ref="B32:F32"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="F35:G35"/>
+    <mergeCell ref="B39:E39"/>
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="F34:G34"/>
     <mergeCell ref="F13:G13"/>
     <mergeCell ref="F14:G14"/>
     <mergeCell ref="B14:C14"/>

--- a/Tagihan/2026/Agustus/Mbg Flamboyan.xlsx
+++ b/Tagihan/2026/Agustus/Mbg Flamboyan.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Data Pekerjaan\Tagihan\2026\Agustus\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\Data-Pekerjaan\Tagihan\2026\Agustus\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9FCA1F01-8371-456C-9210-6DD63E7582AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7AC185DA-0F86-4650-BD1A-1418EE23A542}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Perbaikan" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="36">
   <si>
     <t>NO.</t>
   </si>
@@ -193,29 +193,11 @@
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t xml:space="preserve"> 05 Agustus 2025</t>
+      <t xml:space="preserve"> 07 Agustus 2026</t>
     </r>
   </si>
   <si>
-    <t>Kabel Listrik</t>
-  </si>
-  <si>
-    <t>Kabel LAN</t>
-  </si>
-  <si>
-    <t>Konektor RJ45</t>
-  </si>
-  <si>
-    <t>Steker Female</t>
-  </si>
-  <si>
-    <t>Steker Broco Bulat</t>
-  </si>
-  <si>
-    <t>Barel UTP</t>
-  </si>
-  <si>
-    <t>Perbaikan Dan Reposisi Camera</t>
+    <t>Biaya Perbaikan CCTV</t>
   </si>
 </sst>
 </file>
@@ -223,7 +205,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="42" formatCode="_-&quot;Rp&quot;* #,##0_-;\-&quot;Rp&quot;* #,##0_-;_-&quot;Rp&quot;* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-&quot;Rp&quot;* #,##0_-;\-&quot;Rp&quot;* #,##0_-;_-&quot;Rp&quot;* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
   <fonts count="11" x14ac:knownFonts="1">
     <font>
@@ -576,38 +558,38 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="42" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="42" fontId="10" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -658,7 +640,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -679,11 +661,11 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -761,13 +743,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>238125</xdr:colOff>
-      <xdr:row>32</xdr:row>
+      <xdr:row>33</xdr:row>
       <xdr:rowOff>59532</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>2403475</xdr:colOff>
-      <xdr:row>39</xdr:row>
+      <xdr:row>40</xdr:row>
       <xdr:rowOff>115571</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1265,7 +1247,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B5:H40"/>
+  <dimension ref="B5:H41"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.28515625" customWidth="1"/>
@@ -1378,144 +1360,66 @@
         <v>35</v>
       </c>
       <c r="D17" s="34">
-        <v>21</v>
-      </c>
-      <c r="E17" s="33" t="s">
-        <v>21</v>
+        <v>1</v>
+      </c>
+      <c r="E17" s="34" t="s">
+        <v>16</v>
       </c>
       <c r="F17" s="25">
-        <v>6000</v>
+        <v>100000</v>
       </c>
       <c r="G17" s="25">
-        <f>F17*D17</f>
-        <v>126000</v>
+        <f t="shared" ref="G17:G18" si="0">F17*D17</f>
+        <v>100000</v>
       </c>
     </row>
     <row r="18" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="2">
-        <v>2</v>
-      </c>
-      <c r="C18" s="37" t="s">
-        <v>36</v>
-      </c>
-      <c r="D18" s="2">
-        <v>6</v>
-      </c>
-      <c r="E18" s="26" t="s">
-        <v>21</v>
-      </c>
-      <c r="F18" s="25">
-        <v>5000</v>
-      </c>
-      <c r="G18" s="25">
-        <f t="shared" ref="G18:G23" si="0">F18*D18</f>
-        <v>30000</v>
-      </c>
+      <c r="B18" s="2"/>
+      <c r="C18" s="37"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="25"/>
+      <c r="G18" s="25"/>
     </row>
     <row r="19" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="2">
-        <v>3</v>
-      </c>
-      <c r="C19" s="37" t="s">
-        <v>37</v>
-      </c>
-      <c r="D19" s="2">
-        <v>9</v>
-      </c>
-      <c r="E19" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="F19" s="25">
-        <v>5000</v>
-      </c>
-      <c r="G19" s="25">
-        <f t="shared" si="0"/>
-        <v>45000</v>
-      </c>
+      <c r="B19" s="2"/>
+      <c r="C19" s="37"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="25"/>
+      <c r="G19" s="25"/>
     </row>
     <row r="20" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="2">
-        <v>4</v>
-      </c>
-      <c r="C20" s="37" t="s">
-        <v>38</v>
-      </c>
-      <c r="D20" s="2">
-        <v>3</v>
-      </c>
-      <c r="E20" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="F20" s="25">
-        <v>5000</v>
-      </c>
-      <c r="G20" s="25">
-        <f t="shared" si="0"/>
-        <v>15000</v>
-      </c>
+      <c r="B20" s="2"/>
+      <c r="C20" s="37"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="26"/>
+      <c r="F20" s="25"/>
+      <c r="G20" s="25"/>
     </row>
     <row r="21" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="2">
-        <v>5</v>
-      </c>
-      <c r="C21" s="26" t="s">
-        <v>39</v>
-      </c>
-      <c r="D21" s="2">
-        <v>1</v>
-      </c>
-      <c r="E21" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="F21" s="23">
-        <v>12000</v>
-      </c>
-      <c r="G21" s="25">
-        <f t="shared" si="0"/>
-        <v>12000</v>
-      </c>
+      <c r="B21" s="2"/>
+      <c r="C21" s="26"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="26"/>
+      <c r="F21" s="25"/>
+      <c r="G21" s="25"/>
     </row>
     <row r="22" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="2">
-        <v>6</v>
-      </c>
-      <c r="C22" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="D22" s="2">
-        <v>2</v>
-      </c>
-      <c r="E22" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="F22" s="23">
-        <v>5000</v>
-      </c>
-      <c r="G22" s="25">
-        <f t="shared" si="0"/>
-        <v>10000</v>
-      </c>
+      <c r="B22" s="2"/>
+      <c r="C22" s="26"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="26"/>
+      <c r="F22" s="23"/>
+      <c r="G22" s="25"/>
     </row>
     <row r="23" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="2">
-        <v>7</v>
-      </c>
-      <c r="C23" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="D23" s="2">
-        <v>7</v>
-      </c>
-      <c r="E23" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="F23" s="23">
-        <v>100000</v>
-      </c>
-      <c r="G23" s="25">
-        <f t="shared" si="0"/>
-        <v>700000</v>
-      </c>
+      <c r="B23" s="2"/>
+      <c r="C23" s="26"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="26"/>
+      <c r="F23" s="23"/>
+      <c r="G23" s="25"/>
     </row>
     <row r="24" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="2"/>
@@ -1569,85 +1473,93 @@
       <c r="B30" s="2"/>
       <c r="C30" s="26"/>
       <c r="D30" s="2"/>
-      <c r="E30" s="28"/>
-      <c r="F30" s="25"/>
-      <c r="G30" s="24"/>
-    </row>
-    <row r="31" spans="2:7" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B31" s="47" t="s">
+      <c r="E30" s="26"/>
+      <c r="F30" s="23"/>
+      <c r="G30" s="25"/>
+    </row>
+    <row r="31" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="2"/>
+      <c r="C31" s="26"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="28"/>
+      <c r="F31" s="25"/>
+      <c r="G31" s="24"/>
+    </row>
+    <row r="32" spans="2:7" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B32" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="C31" s="48"/>
-      <c r="D31" s="48"/>
-      <c r="E31" s="48"/>
-      <c r="F31" s="49"/>
-      <c r="G31" s="27">
-        <f>SUM(G17:G30)</f>
-        <v>938000</v>
-      </c>
-    </row>
-    <row r="32" spans="2:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="3"/>
-      <c r="C32" s="3"/>
-      <c r="D32" s="31"/>
-      <c r="E32" s="3"/>
-      <c r="F32" s="16"/>
-      <c r="G32" s="17"/>
-    </row>
-    <row r="34" spans="2:8" s="19" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B34" s="50" t="s">
+      <c r="C32" s="48"/>
+      <c r="D32" s="48"/>
+      <c r="E32" s="48"/>
+      <c r="F32" s="49"/>
+      <c r="G32" s="27">
+        <f>SUM(G17:G31)</f>
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="33" spans="2:8" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="3"/>
+      <c r="C33" s="3"/>
+      <c r="D33" s="31"/>
+      <c r="E33" s="3"/>
+      <c r="F33" s="16"/>
+      <c r="G33" s="17"/>
+    </row>
+    <row r="35" spans="2:8" s="19" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="B35" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="C34" s="50"/>
-      <c r="D34" s="32"/>
-      <c r="E34" s="18"/>
-      <c r="F34" s="51" t="s">
+      <c r="C35" s="50"/>
+      <c r="D35" s="32"/>
+      <c r="E35" s="18"/>
+      <c r="F35" s="51" t="s">
         <v>6</v>
       </c>
-      <c r="G34" s="51"/>
-    </row>
-    <row r="38" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B38" s="41"/>
-      <c r="C38" s="41"/>
-      <c r="D38" s="41"/>
-      <c r="E38" s="41"/>
-      <c r="F38" s="41"/>
-      <c r="G38" s="41"/>
-    </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B39" s="45" t="s">
+      <c r="G35" s="51"/>
+    </row>
+    <row r="39" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B39" s="41"/>
+      <c r="C39" s="41"/>
+      <c r="D39" s="41"/>
+      <c r="E39" s="41"/>
+      <c r="F39" s="41"/>
+      <c r="G39" s="41"/>
+    </row>
+    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B40" s="45" t="s">
         <v>14</v>
       </c>
-      <c r="C39" s="46"/>
-      <c r="D39" s="46"/>
-      <c r="E39" s="46"/>
-      <c r="F39" s="20"/>
-      <c r="G39" s="22"/>
-      <c r="H39" s="21"/>
-    </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B40" s="42" t="s">
+      <c r="C40" s="46"/>
+      <c r="D40" s="46"/>
+      <c r="E40" s="46"/>
+      <c r="F40" s="20"/>
+      <c r="G40" s="22"/>
+      <c r="H40" s="21"/>
+    </row>
+    <row r="41" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B41" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="C40" s="43"/>
-      <c r="D40" s="43"/>
-      <c r="E40" s="43"/>
-      <c r="F40" s="43"/>
-      <c r="G40" s="43"/>
-      <c r="H40" s="21"/>
+      <c r="C41" s="43"/>
+      <c r="D41" s="43"/>
+      <c r="E41" s="43"/>
+      <c r="F41" s="43"/>
+      <c r="G41" s="43"/>
+      <c r="H41" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="13">
     <mergeCell ref="C7:G8"/>
     <mergeCell ref="C9:G9"/>
     <mergeCell ref="C10:G10"/>
-    <mergeCell ref="B38:G38"/>
-    <mergeCell ref="B40:G40"/>
+    <mergeCell ref="B39:G39"/>
+    <mergeCell ref="B41:G41"/>
     <mergeCell ref="C11:G11"/>
-    <mergeCell ref="B39:E39"/>
-    <mergeCell ref="B31:F31"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="F34:G34"/>
+    <mergeCell ref="B40:E40"/>
+    <mergeCell ref="B32:F32"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="F35:G35"/>
     <mergeCell ref="F13:G13"/>
     <mergeCell ref="F14:G14"/>
     <mergeCell ref="B14:C14"/>
